--- a/output/laminas_comunales/comunal_o_ocup_a_2022_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>48.776322134705</v>
+        <v>63.7152777777778</v>
       </c>
     </row>
     <row r="3">
@@ -399,97 +399,1132 @@
         </is>
       </c>
       <c r="C3">
-        <v>46.9966545012165</v>
+        <v>63.3675464320626</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calama</t>
+          <t>Ollagüe</t>
         </is>
       </c>
       <c r="C4">
-        <v>46.3546535150746</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="C5">
-        <v>45.8851024453916</v>
+        <v>62.4523809523809</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C6">
-        <v>45.7352941176471</v>
+        <v>61.679240349416</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C7">
-        <v>36.9225645653388</v>
+        <v>61.5796798256339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C8">
-        <v>36.6706254948535</v>
+        <v>61.3437875539479</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>57.5910811450201</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>57.3503103569783</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>57.2907467373172</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>57.024474627857</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>56.9877765141036</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>56.4160728125323</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>55.9274755927476</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>2301</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Tocopilla</t>
         </is>
       </c>
-      <c r="C9">
+      <c r="C16">
+        <v>55.5068017503805</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>54.998778002195</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>54.5851267336203</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>54.4921875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>54.043048907792</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>53.8840599483439</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>53.7289605845775</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>53.5535663540779</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>49.3428704349849</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>48.8888888888889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>48.776322134705</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>48.6831852890759</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>47.7477477477477</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>47.4733207784055</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>46.9966545012165</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>46.8992248062016</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>46.6666666666667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>46.5918247179869</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>46.3546535150746</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>45.8851024453916</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>45.7352941176471</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>45.7144800322649</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>45.4087401794404</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>44.7866789441375</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>44.5436507936508</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>41.8525039123631</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>40.4252283105023</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>39.569822741029</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>39.0008223684211</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>38.7820512820513</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>38.5342894239849</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>38.433188805676</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>38.1455214079328</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>38.0342462880631</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>37.7922175858428</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>37.7285056597916</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>37.6585970541053</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>37.5623815688261</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>37.4802081841188</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>37.0111605838118</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>36.9225645653388</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>36.6706254948535</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C58">
         <v>36.5693333956765</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>36.2298195631529</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>35.077472215462</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>33.6840832123851</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>32.7561434799841</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>31.5011609215931</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>30.0227899724121</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>28.0209355577363</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>27.9569892473118</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>27.939534141672</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>26.4289969585803</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>24.7835497835498</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>21.2901701323251</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>16.7412818709795</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>16.6478218802034</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>16.3211259878243</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>15.9787248932745</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>14.5841771297421</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>14.287972864206</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>12.8098628691983</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>9.912280701754391</v>
       </c>
     </row>
   </sheetData>
